--- a/Resources/entity_template.xlsx
+++ b/Resources/entity_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaewo\Desktop\work\mapper\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB42644D-A898-4FC7-A9BA-60F47B2E51B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B9C86-0120-4CEE-B239-2BA1249C832B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="948" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entity 작성요령" sheetId="33" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="280">
   <si>
     <t xml:space="preserve"> (a) 순조세비용의 가산(「국제조세조정에 관한 법률 시행규칙」 별표 1 제1호)</t>
   </si>
@@ -751,14 +751,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1.1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신고구성기업 상호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>항목번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -771,544 +763,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>납세자번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.1.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>납세자번호, 납세자번호 유형, 발급국가를 컴마로 구분하여 기재
-납세자번호 유형
-GIR3001: Tax Identification Number
-GIR3002: Functionally equivalent number
-GIR3003: Agreed GIR designated number
-GIR3004: Not required to be reported
-발급국가 ISO3166-alpha2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.1.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신고구성기업 지위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>시트명</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>다국적기업그룹 정보</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR401: UPE
-GIR402: Designated Filing Entity
-GIR403: Designated Local Entity
-GIR404: Constituent Entity
-GIR405: Other</t>
-  </si>
-  <si>
-    <t>1.1.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신고구성기업 소재지국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>복수선택</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ISO3166-alpha2 예시) KR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.1.6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연례 자동정보 교환당사국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>가능(컴마로 구분)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1.2.2.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종모기업 연결재무제표(유형)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MR 54~55p Consolidated FS 정의
-GIR501: (a)
-GIR502: (b)
-GIR503: (c)
-GIR504: (d)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2.2.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종모기업 연결재무제표 통화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ISO4217-alpha3 예시) KRW</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종모기업</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>적용가능규칙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR201: QIIR ─ 다른 소재지국 저율과세구성기업에만 적용
-GIR202: QIIR ─ 다른 소재지국 + 모기업 소재지국 저율과세구성기업 모두 적용
-GIR203: QUTPR
-GIR204: QDMTT
-GIR205: Not Applicable</t>
-  </si>
-  <si>
-    <t>1.3.1.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종모기업 납세자번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.1.6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>글로벌최저한세 목적상 기업유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR701: Constituent Entity
-GIR702: Flow-Through Entity - Tax Transparent
-GIR703: Flow-Through Entity - Reverse Hybrid
-GIR704: Hybrid Entity
-GIR705: Permanent Establishment
-GIR706: Main Entity
-GIR707: Minority-Owned Parent Entity
-GIR708: Minority-Owned Subsidiary
-GIR709: Minority-Owned Constituent ENtity
-GIR710: Investment Entity
-GIR711: Insurance Investment Entity
-GIR712: Securitisation Entity
-GIR713: JV
-GIR714: JV Subsidiary
-GIR715: Non-Material Constituent Entity
-GIR716: POPE
-GIR717: Intermediate Parent Entity
-GIR718: Ultimate Parent Entity
-GIR719: Excluded Entity
-GIR720: Parent Entity Required to apply a QIIR under Art 10.3.5
-GIR721: Non-Group member</t>
-  </si>
-  <si>
-    <t>1.3.1.7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제외기업 유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR601: Governmental Entity
-GIR602: International Organisation
-GIR603: Non-profit Organisation
-GIR604: Pension Fund
-GIR605: Investment Fund that is an UPE
-GIR606: Real Estate Investment Vehicle that is an UPE</t>
-  </si>
-  <si>
-    <t>1.3.1.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>국조령 제103조제4항 적용 국가에 해당되는 경우</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>소재지국</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹구조</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>구성기업, 공동기업 또는 공동기업 자회사의 상호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR801: UPE
-GIR802: Constituent Entities
-GIR803: JVs
-GIR804: JV Subsidiaries
-GIR805: Excluded Entities (aggregate)
-GIR806: Non-Group members (aggregate)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.11</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모기업 유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR901: POPE
-GIR902: Intermediate Parent Entity
-GIR903: Parent Entity required to apply a QIIR under Art. 10.3.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.12</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.1.13</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art2.1.3에 따른 모기업의 납세자번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art2.1.5에 따른 모기업의 납세자번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.2.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제외기업</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>제외기업 상호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.2.2.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1001: Governmental Entity
-GIR1002: International Organisation
-GIR1003: Non-profit Organisation
-GIR1004: Pension Fund
-GIR1005: Investment Fund that is an UPE
-GIR1006: Real Estate Investment Vehicle that is an UPE
-GIR1007: Entity owned by Excluded Entities under Article 1.5.2(a)
-GIR1008: Entity owned by Excluded Entities under Article 1.5.2(b)</t>
-  </si>
-  <si>
-    <t>1.3.3.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>구성기업 (또는 다국적기업그룹의 다른 기업) 또는 공동기업그룹기업의 상호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그룹구조 변동</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.3.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>변동 전 글로벌최저한세목적상 기업 유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.3.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.3.3.9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주주기업 유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>서식에는 없으나 XML에 존재하는 내용입니다.
-GIR801: UPE
-GIR802: Constituent Entities
-GIR803: JVs
-GIR804: JV Subsidiaries
-GIR805: Excluded Entities (aggregate)
-GIR806: Non-Group members (aggregate)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>요약</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1101: Constituent Entities
-GIR1102: Minority-Owned Subgroup
-GIR1103: Standalone MOCEs
-GIR1104: Investment Entities
-GIR1105: JV Group
-GIR1106: Stateless Constituent Entity</t>
-  </si>
-  <si>
-    <t>하위그룹 유형</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>하위그룹 최상위기업 납세자번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>글로벌최저한세 과세권이 있는 국가명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가능(세미콜론으로 구분)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>국가코드: ISO3166-alpha2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>적용면제 또는 제외 사유</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1201: De minimis Exclusion
-GIR1202: QDMTT safe harbour
-GIR1203: Transitional CbCR Safe Harbour - De minimis test
-GIR1204: Transitional CbCR Safe Harbour - ETR test
-GIR1205: Transitional CbCR Safe Harbour - Routine profit test
-GIR1206: Transitional UTPR Safe Harbour
-GIR1207: Permanent Safe Harbour - De minimis test
-GIR1208: Permanent Safe Harbour - ETR test
-GIR1209: Permanent Safe Harbour - Routine profit test</t>
-  </si>
-  <si>
-    <t>실효세율 범위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1301: below 2.5%
-GIR1302: 2.5% or above but below 5%
-GIR1303: 5% or above but below 7.5%
-GIR1304: 7.5% or above but below 10%
-GIR1305: 10% or above but below 12.5%
-GIR1306: 12.5% or above but below 15%
-GIR1307: 15% or above but below 17.5%
-GIR1308: 17.5% or above but below 20%
-GIR1309: 20% or above but below 22.5%
-GIR1310: 22.5% or above but below 25%
-GIR1311: 25% or above but below 27.5%
-GIR1312: 27.5% or above but below 30%
-GIR1313: 30% or above
-GIR1314: Section 3.2 not completed</t>
-  </si>
-  <si>
-    <t>1.4.8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.4.9</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가세액 (적격소재국추가세) 범위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1401: No Top-up Tax payable
-GIR1402: below EUR 1 million
-GIR1403: EUR 1 million to below EUR 5 million
-GIR1404: EUR 5 million to below EUR 25 million
-GIR1405: EUR 25 million to below EUR 50 million
-GIR1406: EUR 50 million to below EUR 75 million
-GIR1407: EUR 75 million to below EUR 100 million
-GIR1408: EUR 100 million to below EUR 250 million
-GIR1409: EUR 250 million or above</t>
-  </si>
-  <si>
-    <t>추가세액(글로벌최저한세) 범위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GIR1501: No Top-up Tax payable
-GIR1502: below EUR 1 million
-GIR1503: EUR 1 million to below EUR 5 million
-GIR1504: EUR 5 million to below EUR 25 million
-GIR1505: EUR 25 million to below EUR 50 million
-GIR1506: EUR 50 million to below EUR 75 million
-GIR1507: EUR 75 million to below EUR 100 million
-GIR1508: EUR 100 million to below EUR 250 million
-GIR1509: EUR 250 million or above</t>
-  </si>
-  <si>
-    <t>2.1.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>소재지국(국가명)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.1.4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>과세권이 있는 국가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>적용면제</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>국가코드, 하위그룹 유형, 하위그룹 최상위기업 납세자번호, 하위그룹 최상위기업 납세자번호 유형, 하위그룹 최상위기업 납세자번호 발급국가코드를 컴마로 구분하여 기재
-국가코드: ISO3166-alpha2
-납세자번호 유형
-GIR3001: Tax Identification Number
-GIR3002: Functionally equivalent number
-GIR3003: Agreed GIR designated number
-GIR3004: Not required to be reported
-하위그룹 유형
-GIR1101: Constituent Entities
-GIR1102: Minority-Owned Subgroup
-GIR1103: Standalone MOCEs
-GIR1104: Investment Entities
-GIR1105: JV Group
-GIR1106: Stateless Constituent Entity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.3.2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>준거국가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.3.5 a</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.4.3.1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UTPR 배분</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>소득산입보완규칙 시행국가</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>영문명을 기재합니다.
-국문명도 기재하고자 하는 경우 영문명, 국문명을 세미콜론(;)을 기준으로 구분하여 기재합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>영문명을 기재합니다. 국문명도 기재하고자 하는 경우 영문명, 국문명을 세미콜론(;)을 기준으로 구분하여 기재합니다.</t>
-  </si>
-  <si>
-    <t>영문명을 기재합니다. 
-국문명도 기재하고자 하는 경우 영문명, 국문명을 세미콜론(;)을 기준으로 구분하여 기재합니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1653,6 +1120,42 @@
   </si>
   <si>
     <t>최종모기업의 연결재무제표 작성 회계기준 외의 회계기준에 따라 계산된 회계상 순손익을 사용하는 구성기업(또는 공동기업그룹 기업)의 납세자번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4.1.1a</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저율과세구성기업 또는 저율과세 공동기업그룹 기업의 납세자번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가세액</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4.1.2a</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모기업</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모기업 소재지국</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4.1.2b</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4.2.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「국제조세조정에 관한 법률」 제73조제3항제1호에 해당하지 않는 저율과세구성기업 또는 저율과세 공동기업그룹 기업의 납세자번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1759,7 +1262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1920,15 +1423,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1948,7 +1442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2051,7 +1545,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2080,9 +1574,6 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2128,31 +1619,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2188,6 +1664,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2528,7 +2019,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="B2:F71"/>
+  <dimension ref="B2:F31"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -2541,101 +2032,99 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="11" t="s">
+      <c r="E3" s="17" t="s">
         <v>218</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>317</v>
       </c>
       <c r="F3" s="11"/>
     </row>
     <row r="4" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>214</v>
-      </c>
       <c r="F4" s="11"/>
     </row>
-    <row r="5" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="2:6" ht="70.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>227</v>
@@ -2648,9 +2137,9 @@
       </c>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>230</v>
@@ -2659,205 +2148,193 @@
         <v>231</v>
       </c>
       <c r="E9" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="2:6" ht="35.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="11" t="s">
+      <c r="D10" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>226</v>
-      </c>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="11" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="11"/>
+    </row>
+    <row r="13" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="2:6" ht="193.3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D14" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="2:6" ht="246" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="D15" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D12" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="E15" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D13" s="16" t="s">
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="E17" s="17" t="s">
         <v>247</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>319</v>
       </c>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="D20" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>256</v>
-      </c>
       <c r="E20" s="17" t="s">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="11" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F21" s="11"/>
     </row>
-    <row r="22" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="11" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>259</v>
@@ -2866,82 +2343,84 @@
         <v>260</v>
       </c>
       <c r="E22" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F23" s="11"/>
-    </row>
-    <row r="24" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="F23" s="11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="11" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>263</v>
       </c>
       <c r="D24" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="E24" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="25" spans="2:6" ht="52.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="11" t="s">
+      <c r="D25" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="F25" s="11"/>
-    </row>
-    <row r="26" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="E26" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="D27" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="F26" s="11"/>
-    </row>
-    <row r="27" spans="2:6" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>272</v>
-      </c>
       <c r="E27" s="17" t="s">
-        <v>318</v>
+        <v>218</v>
       </c>
       <c r="F27" s="11"/>
     </row>
@@ -2950,34 +2429,32 @@
         <v>273</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F28" s="11"/>
     </row>
-    <row r="29" spans="2:6" ht="369" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="11" t="s">
         <v>273</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" ht="140.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" s="86" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="11" t="s">
         <v>273</v>
       </c>
@@ -2985,620 +2462,27 @@
         <v>277</v>
       </c>
       <c r="D30" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="D31" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B31" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>223</v>
+      <c r="E31" s="86" t="s">
+        <v>218</v>
       </c>
       <c r="F31" s="11"/>
-    </row>
-    <row r="32" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B32" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="F32" s="11"/>
-    </row>
-    <row r="33" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F33" s="11"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="246" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="F36" s="11"/>
-    </row>
-    <row r="37" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B37" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="F37" s="11"/>
-    </row>
-    <row r="38" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="F38" s="11"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F39" s="11"/>
-    </row>
-    <row r="40" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="F40" s="11"/>
-    </row>
-    <row r="41" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="F41" s="11"/>
-    </row>
-    <row r="42" spans="2:6" ht="333.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F43" s="11"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F44" s="11"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="F45" s="11"/>
-    </row>
-    <row r="47" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F47" s="11"/>
-    </row>
-    <row r="48" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F48" s="11"/>
-    </row>
-    <row r="49" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F49" s="11"/>
-    </row>
-    <row r="50" spans="2:6" ht="70.3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F50" s="11"/>
-    </row>
-    <row r="51" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F51" s="11"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="F52" s="11"/>
-    </row>
-    <row r="53" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F53" s="11"/>
-    </row>
-    <row r="54" spans="2:6" ht="35.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>339</v>
-      </c>
-      <c r="F54" s="11"/>
-    </row>
-    <row r="55" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F55" s="11"/>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="F56" s="11"/>
-    </row>
-    <row r="57" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F57" s="11"/>
-    </row>
-    <row r="58" spans="2:6" ht="193.3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="F58" s="11"/>
-    </row>
-    <row r="59" spans="2:6" ht="246" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="F59" s="11"/>
-    </row>
-    <row r="60" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F60" s="11"/>
-    </row>
-    <row r="61" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="F61" s="11"/>
-    </row>
-    <row r="62" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F62" s="11"/>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="F63" s="11"/>
-    </row>
-    <row r="64" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F64" s="11"/>
-    </row>
-    <row r="65" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F65" s="11"/>
-    </row>
-    <row r="66" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E66" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F66" s="11"/>
-    </row>
-    <row r="67" spans="2:6" ht="105.45" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="87.9" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E68" s="17" t="s">
-        <v>370</v>
-      </c>
-      <c r="F68" s="11"/>
-    </row>
-    <row r="69" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F69" s="11"/>
-    </row>
-    <row r="70" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>373</v>
-      </c>
-      <c r="E70" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F70" s="11"/>
-    </row>
-    <row r="71" spans="2:6" ht="158.15" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F71" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4964,7 +3848,7 @@
       <c r="L69" s="25"/>
       <c r="M69" s="25"/>
       <c r="N69" s="25"/>
-      <c r="O69" s="77"/>
+      <c r="O69" s="71"/>
       <c r="P69" s="25"/>
       <c r="Q69" s="25"/>
       <c r="R69" s="25"/>
@@ -4985,17 +3869,17 @@
       <c r="L70" s="25"/>
       <c r="M70" s="25"/>
       <c r="N70" s="36"/>
-      <c r="O70" s="51" t="s">
+      <c r="O70" s="50" t="s">
         <v>39</v>
       </c>
       <c r="P70" s="27"/>
-      <c r="Q70" s="78" t="s">
+      <c r="Q70" s="72" t="s">
         <v>40</v>
       </c>
       <c r="R70" s="25"/>
     </row>
     <row r="71" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="52" t="s">
+      <c r="B71" s="51" t="s">
         <v>75</v>
       </c>
       <c r="C71" s="25"/>
@@ -5012,11 +3896,11 @@
       <c r="N71" s="36"/>
       <c r="O71" s="34"/>
       <c r="P71" s="27"/>
-      <c r="Q71" s="77"/>
+      <c r="Q71" s="71"/>
       <c r="R71" s="25"/>
     </row>
     <row r="72" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="52" t="s">
+      <c r="B72" s="51" t="s">
         <v>76</v>
       </c>
       <c r="C72" s="25"/>
@@ -5033,11 +3917,11 @@
       <c r="N72" s="36"/>
       <c r="O72" s="34"/>
       <c r="P72" s="27"/>
-      <c r="Q72" s="77"/>
+      <c r="Q72" s="71"/>
       <c r="R72" s="25"/>
     </row>
     <row r="73" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="52" t="s">
+      <c r="B73" s="51" t="s">
         <v>77</v>
       </c>
       <c r="C73" s="25"/>
@@ -5054,11 +3938,11 @@
       <c r="N73" s="36"/>
       <c r="O73" s="34"/>
       <c r="P73" s="27"/>
-      <c r="Q73" s="77"/>
+      <c r="Q73" s="71"/>
       <c r="R73" s="25"/>
     </row>
     <row r="74" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="52" t="s">
+      <c r="B74" s="51" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="25"/>
@@ -5075,11 +3959,11 @@
       <c r="N74" s="36"/>
       <c r="O74" s="34"/>
       <c r="P74" s="27"/>
-      <c r="Q74" s="77"/>
+      <c r="Q74" s="71"/>
       <c r="R74" s="25"/>
     </row>
     <row r="75" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="52" t="s">
+      <c r="B75" s="51" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="25"/>
@@ -5096,11 +3980,11 @@
       <c r="N75" s="36"/>
       <c r="O75" s="34"/>
       <c r="P75" s="27"/>
-      <c r="Q75" s="77"/>
+      <c r="Q75" s="71"/>
       <c r="R75" s="25"/>
     </row>
     <row r="76" spans="2:18" ht="28.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="52" t="s">
+      <c r="B76" s="51" t="s">
         <v>80</v>
       </c>
       <c r="C76" s="25"/>
@@ -5117,11 +4001,11 @@
       <c r="N76" s="36"/>
       <c r="O76" s="34"/>
       <c r="P76" s="27"/>
-      <c r="Q76" s="77"/>
+      <c r="Q76" s="71"/>
       <c r="R76" s="25"/>
     </row>
     <row r="77" spans="2:18" ht="32.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="52" t="s">
+      <c r="B77" s="51" t="s">
         <v>81</v>
       </c>
       <c r="C77" s="25"/>
@@ -5138,11 +4022,11 @@
       <c r="N77" s="36"/>
       <c r="O77" s="34"/>
       <c r="P77" s="27"/>
-      <c r="Q77" s="77"/>
+      <c r="Q77" s="71"/>
       <c r="R77" s="25"/>
     </row>
     <row r="78" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="52" t="s">
+      <c r="B78" s="51" t="s">
         <v>82</v>
       </c>
       <c r="C78" s="25"/>
@@ -5159,11 +4043,11 @@
       <c r="N78" s="36"/>
       <c r="O78" s="34"/>
       <c r="P78" s="27"/>
-      <c r="Q78" s="77"/>
+      <c r="Q78" s="71"/>
       <c r="R78" s="25"/>
     </row>
     <row r="79" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="52" t="s">
+      <c r="B79" s="51" t="s">
         <v>83</v>
       </c>
       <c r="C79" s="25"/>
@@ -5180,11 +4064,11 @@
       <c r="N79" s="36"/>
       <c r="O79" s="34"/>
       <c r="P79" s="27"/>
-      <c r="Q79" s="77"/>
+      <c r="Q79" s="71"/>
       <c r="R79" s="25"/>
     </row>
     <row r="80" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="52" t="s">
+      <c r="B80" s="51" t="s">
         <v>84</v>
       </c>
       <c r="C80" s="25"/>
@@ -5201,11 +4085,11 @@
       <c r="N80" s="36"/>
       <c r="O80" s="34"/>
       <c r="P80" s="27"/>
-      <c r="Q80" s="77"/>
+      <c r="Q80" s="71"/>
       <c r="R80" s="25"/>
     </row>
     <row r="81" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="52" t="s">
+      <c r="B81" s="51" t="s">
         <v>85</v>
       </c>
       <c r="C81" s="25"/>
@@ -5222,11 +4106,11 @@
       <c r="N81" s="36"/>
       <c r="O81" s="34"/>
       <c r="P81" s="27"/>
-      <c r="Q81" s="77"/>
+      <c r="Q81" s="71"/>
       <c r="R81" s="25"/>
     </row>
     <row r="82" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="52" t="s">
+      <c r="B82" s="51" t="s">
         <v>86</v>
       </c>
       <c r="C82" s="25"/>
@@ -5243,11 +4127,11 @@
       <c r="N82" s="36"/>
       <c r="O82" s="34"/>
       <c r="P82" s="27"/>
-      <c r="Q82" s="77"/>
+      <c r="Q82" s="71"/>
       <c r="R82" s="25"/>
     </row>
     <row r="83" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="52" t="s">
+      <c r="B83" s="51" t="s">
         <v>87</v>
       </c>
       <c r="C83" s="25"/>
@@ -5264,11 +4148,11 @@
       <c r="N83" s="36"/>
       <c r="O83" s="34"/>
       <c r="P83" s="27"/>
-      <c r="Q83" s="77"/>
+      <c r="Q83" s="71"/>
       <c r="R83" s="25"/>
     </row>
     <row r="84" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="52" t="s">
+      <c r="B84" s="51" t="s">
         <v>88</v>
       </c>
       <c r="C84" s="25"/>
@@ -5285,11 +4169,11 @@
       <c r="N84" s="36"/>
       <c r="O84" s="34"/>
       <c r="P84" s="27"/>
-      <c r="Q84" s="77"/>
+      <c r="Q84" s="71"/>
       <c r="R84" s="25"/>
     </row>
     <row r="85" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="52" t="s">
+      <c r="B85" s="51" t="s">
         <v>89</v>
       </c>
       <c r="C85" s="25"/>
@@ -5306,11 +4190,11 @@
       <c r="N85" s="36"/>
       <c r="O85" s="34"/>
       <c r="P85" s="27"/>
-      <c r="Q85" s="77"/>
+      <c r="Q85" s="71"/>
       <c r="R85" s="25"/>
     </row>
     <row r="86" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" s="52" t="s">
+      <c r="B86" s="51" t="s">
         <v>90</v>
       </c>
       <c r="C86" s="25"/>
@@ -5327,11 +4211,11 @@
       <c r="N86" s="36"/>
       <c r="O86" s="34"/>
       <c r="P86" s="27"/>
-      <c r="Q86" s="77"/>
+      <c r="Q86" s="71"/>
       <c r="R86" s="25"/>
     </row>
     <row r="87" spans="2:18" ht="31.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" s="52" t="s">
+      <c r="B87" s="51" t="s">
         <v>91</v>
       </c>
       <c r="C87" s="25"/>
@@ -5348,7 +4232,7 @@
       <c r="N87" s="36"/>
       <c r="O87" s="34"/>
       <c r="P87" s="27"/>
-      <c r="Q87" s="79"/>
+      <c r="Q87" s="73"/>
       <c r="R87" s="19"/>
     </row>
     <row r="88" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -5367,7 +4251,7 @@
       <c r="L88" s="25"/>
       <c r="M88" s="25"/>
       <c r="N88" s="25"/>
-      <c r="O88" s="77">
+      <c r="O88" s="71">
         <f>O69+SUM(O71:P87)-SUM(Q71:R87)</f>
         <v>0</v>
       </c>
@@ -5428,7 +4312,7 @@
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="44" t="s">
-        <v>354</v>
+        <v>248</v>
       </c>
       <c r="H91" s="30"/>
       <c r="I91" s="32"/>
@@ -5512,7 +4396,7 @@
       <c r="R95" s="25"/>
     </row>
     <row r="96" spans="2:18" ht="22.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B96" s="82" t="s">
+      <c r="B96" s="76" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="25"/>
@@ -5527,7 +4411,7 @@
       <c r="L96" s="25"/>
       <c r="M96" s="25"/>
       <c r="N96" s="27"/>
-      <c r="O96" s="80"/>
+      <c r="O96" s="74"/>
       <c r="P96" s="25"/>
       <c r="Q96" s="25"/>
       <c r="R96" s="25"/>
@@ -5548,17 +4432,17 @@
       <c r="L97" s="25"/>
       <c r="M97" s="25"/>
       <c r="N97" s="36"/>
-      <c r="O97" s="51" t="s">
+      <c r="O97" s="50" t="s">
         <v>39</v>
       </c>
       <c r="P97" s="27"/>
-      <c r="Q97" s="78" t="s">
+      <c r="Q97" s="72" t="s">
         <v>40</v>
       </c>
       <c r="R97" s="25"/>
     </row>
     <row r="98" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B98" s="52" t="s">
+      <c r="B98" s="51" t="s">
         <v>19</v>
       </c>
       <c r="C98" s="25"/>
@@ -5575,11 +4459,11 @@
       <c r="N98" s="36"/>
       <c r="O98" s="34"/>
       <c r="P98" s="27"/>
-      <c r="Q98" s="77"/>
+      <c r="Q98" s="71"/>
       <c r="R98" s="25"/>
     </row>
     <row r="99" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B99" s="52" t="s">
+      <c r="B99" s="51" t="s">
         <v>102</v>
       </c>
       <c r="C99" s="25"/>
@@ -5596,11 +4480,11 @@
       <c r="N99" s="36"/>
       <c r="O99" s="34"/>
       <c r="P99" s="27"/>
-      <c r="Q99" s="77"/>
+      <c r="Q99" s="71"/>
       <c r="R99" s="25"/>
     </row>
     <row r="100" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="52" t="s">
+      <c r="B100" s="51" t="s">
         <v>103</v>
       </c>
       <c r="C100" s="25"/>
@@ -5617,11 +4501,11 @@
       <c r="N100" s="36"/>
       <c r="O100" s="34"/>
       <c r="P100" s="27"/>
-      <c r="Q100" s="77"/>
+      <c r="Q100" s="71"/>
       <c r="R100" s="25"/>
     </row>
     <row r="101" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B101" s="52" t="s">
+      <c r="B101" s="51" t="s">
         <v>104</v>
       </c>
       <c r="C101" s="25"/>
@@ -5638,11 +4522,11 @@
       <c r="N101" s="36"/>
       <c r="O101" s="34"/>
       <c r="P101" s="27"/>
-      <c r="Q101" s="77"/>
+      <c r="Q101" s="71"/>
       <c r="R101" s="25"/>
     </row>
     <row r="102" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="52" t="s">
+      <c r="B102" s="51" t="s">
         <v>105</v>
       </c>
       <c r="C102" s="25"/>
@@ -5659,11 +4543,11 @@
       <c r="N102" s="36"/>
       <c r="O102" s="34"/>
       <c r="P102" s="27"/>
-      <c r="Q102" s="77"/>
+      <c r="Q102" s="71"/>
       <c r="R102" s="25"/>
     </row>
     <row r="103" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="52" t="s">
+      <c r="B103" s="51" t="s">
         <v>106</v>
       </c>
       <c r="C103" s="25"/>
@@ -5680,11 +4564,11 @@
       <c r="N103" s="36"/>
       <c r="O103" s="34"/>
       <c r="P103" s="27"/>
-      <c r="Q103" s="77"/>
+      <c r="Q103" s="71"/>
       <c r="R103" s="25"/>
     </row>
     <row r="104" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="52" t="s">
+      <c r="B104" s="51" t="s">
         <v>20</v>
       </c>
       <c r="C104" s="25"/>
@@ -5701,11 +4585,11 @@
       <c r="N104" s="36"/>
       <c r="O104" s="34"/>
       <c r="P104" s="27"/>
-      <c r="Q104" s="77"/>
+      <c r="Q104" s="71"/>
       <c r="R104" s="25"/>
     </row>
     <row r="105" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="52" t="s">
+      <c r="B105" s="51" t="s">
         <v>21</v>
       </c>
       <c r="C105" s="25"/>
@@ -5722,11 +4606,11 @@
       <c r="N105" s="36"/>
       <c r="O105" s="34"/>
       <c r="P105" s="27"/>
-      <c r="Q105" s="77"/>
+      <c r="Q105" s="71"/>
       <c r="R105" s="25"/>
     </row>
     <row r="106" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="52" t="s">
+      <c r="B106" s="51" t="s">
         <v>22</v>
       </c>
       <c r="C106" s="25"/>
@@ -5743,11 +4627,11 @@
       <c r="N106" s="36"/>
       <c r="O106" s="34"/>
       <c r="P106" s="27"/>
-      <c r="Q106" s="76"/>
-      <c r="R106" s="75"/>
+      <c r="Q106" s="70"/>
+      <c r="R106" s="68"/>
     </row>
     <row r="107" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="52" t="s">
+      <c r="B107" s="51" t="s">
         <v>107</v>
       </c>
       <c r="C107" s="25"/>
@@ -5764,11 +4648,11 @@
       <c r="N107" s="36"/>
       <c r="O107" s="34"/>
       <c r="P107" s="27"/>
-      <c r="Q107" s="77"/>
+      <c r="Q107" s="71"/>
       <c r="R107" s="25"/>
     </row>
     <row r="108" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B108" s="52" t="s">
+      <c r="B108" s="51" t="s">
         <v>23</v>
       </c>
       <c r="C108" s="25"/>
@@ -5785,11 +4669,11 @@
       <c r="N108" s="36"/>
       <c r="O108" s="34"/>
       <c r="P108" s="27"/>
-      <c r="Q108" s="77"/>
+      <c r="Q108" s="71"/>
       <c r="R108" s="25"/>
     </row>
     <row r="109" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="52" t="s">
+      <c r="B109" s="51" t="s">
         <v>24</v>
       </c>
       <c r="C109" s="25"/>
@@ -5806,11 +4690,11 @@
       <c r="N109" s="36"/>
       <c r="O109" s="34"/>
       <c r="P109" s="27"/>
-      <c r="Q109" s="77"/>
+      <c r="Q109" s="71"/>
       <c r="R109" s="25"/>
     </row>
     <row r="110" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B110" s="52" t="s">
+      <c r="B110" s="51" t="s">
         <v>108</v>
       </c>
       <c r="C110" s="25"/>
@@ -5827,11 +4711,11 @@
       <c r="N110" s="36"/>
       <c r="O110" s="34"/>
       <c r="P110" s="27"/>
-      <c r="Q110" s="77"/>
+      <c r="Q110" s="71"/>
       <c r="R110" s="25"/>
     </row>
     <row r="111" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="52" t="s">
+      <c r="B111" s="51" t="s">
         <v>25</v>
       </c>
       <c r="C111" s="25"/>
@@ -5848,11 +4732,11 @@
       <c r="N111" s="36"/>
       <c r="O111" s="34"/>
       <c r="P111" s="27"/>
-      <c r="Q111" s="77"/>
+      <c r="Q111" s="71"/>
       <c r="R111" s="25"/>
     </row>
     <row r="112" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B112" s="52" t="s">
+      <c r="B112" s="51" t="s">
         <v>26</v>
       </c>
       <c r="C112" s="25"/>
@@ -5869,11 +4753,11 @@
       <c r="N112" s="36"/>
       <c r="O112" s="34"/>
       <c r="P112" s="27"/>
-      <c r="Q112" s="77"/>
+      <c r="Q112" s="71"/>
       <c r="R112" s="25"/>
     </row>
     <row r="113" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="52" t="s">
+      <c r="B113" s="51" t="s">
         <v>27</v>
       </c>
       <c r="C113" s="25"/>
@@ -5890,11 +4774,11 @@
       <c r="N113" s="36"/>
       <c r="O113" s="34"/>
       <c r="P113" s="27"/>
-      <c r="Q113" s="79"/>
+      <c r="Q113" s="73"/>
       <c r="R113" s="19"/>
     </row>
     <row r="114" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="82" t="s">
+      <c r="B114" s="76" t="s">
         <v>109</v>
       </c>
       <c r="C114" s="25"/>
@@ -5909,13 +4793,13 @@
       <c r="L114" s="25"/>
       <c r="M114" s="25"/>
       <c r="N114" s="27"/>
-      <c r="O114" s="77"/>
+      <c r="O114" s="71"/>
       <c r="P114" s="25"/>
       <c r="Q114" s="25"/>
       <c r="R114" s="25"/>
     </row>
     <row r="115" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="81" t="s">
+      <c r="B115" s="75" t="s">
         <v>110</v>
       </c>
       <c r="C115" s="25"/>
@@ -5936,7 +4820,7 @@
       <c r="R115" s="25"/>
     </row>
     <row r="116" spans="2:18" ht="21.45" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B116" s="82" t="s">
+      <c r="B116" s="76" t="s">
         <v>111</v>
       </c>
       <c r="C116" s="25"/>
@@ -5951,7 +4835,7 @@
       <c r="L116" s="25"/>
       <c r="M116" s="25"/>
       <c r="N116" s="27"/>
-      <c r="O116" s="77" cm="1">
+      <c r="O116" s="71" cm="1">
         <f t="array" ref="O116">O96+SUM(O98:P113)-SUM(Q98:R113+O114+O115)</f>
         <v>0</v>
       </c>
@@ -6002,10 +4886,10 @@
       <c r="R119" s="25"/>
     </row>
     <row r="120" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="83" t="s">
+      <c r="B120" s="77" t="s">
         <v>114</v>
       </c>
-      <c r="C120" s="84" t="s">
+      <c r="C120" s="78" t="s">
         <v>115</v>
       </c>
       <c r="D120" s="30"/>
@@ -6025,8 +4909,8 @@
       <c r="R120" s="25"/>
     </row>
     <row r="121" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B121" s="54"/>
-      <c r="C121" s="55" t="s">
+      <c r="B121" s="53"/>
+      <c r="C121" s="54" t="s">
         <v>116</v>
       </c>
       <c r="D121" s="25"/>
@@ -6047,7 +4931,7 @@
     </row>
     <row r="122" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B122" s="32"/>
-      <c r="C122" s="55" t="s">
+      <c r="C122" s="54" t="s">
         <v>117</v>
       </c>
       <c r="D122" s="25"/>
@@ -6067,10 +4951,10 @@
       <c r="R122" s="25"/>
     </row>
     <row r="123" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="53" t="s">
+      <c r="B123" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="C123" s="55"/>
+      <c r="C123" s="54"/>
       <c r="D123" s="25"/>
       <c r="E123" s="25"/>
       <c r="F123" s="25"/>
@@ -6082,18 +4966,18 @@
       <c r="L123" s="25"/>
       <c r="M123" s="25"/>
       <c r="N123" s="36"/>
-      <c r="O123" s="51" t="s">
+      <c r="O123" s="50" t="s">
         <v>119</v>
       </c>
       <c r="P123" s="27"/>
-      <c r="Q123" s="78" t="s">
+      <c r="Q123" s="72" t="s">
         <v>120</v>
       </c>
       <c r="R123" s="25"/>
     </row>
     <row r="124" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B124" s="54"/>
-      <c r="C124" s="55" t="s">
+      <c r="B124" s="53"/>
+      <c r="C124" s="54" t="s">
         <v>121</v>
       </c>
       <c r="D124" s="25"/>
@@ -6113,8 +4997,8 @@
       <c r="R124" s="25"/>
     </row>
     <row r="125" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="54"/>
-      <c r="C125" s="55" t="s">
+      <c r="B125" s="53"/>
+      <c r="C125" s="54" t="s">
         <v>122</v>
       </c>
       <c r="D125" s="25"/>
@@ -6134,8 +5018,8 @@
       <c r="R125" s="25"/>
     </row>
     <row r="126" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="54"/>
-      <c r="C126" s="55" t="s">
+      <c r="B126" s="53"/>
+      <c r="C126" s="54" t="s">
         <v>123</v>
       </c>
       <c r="D126" s="25"/>
@@ -6155,8 +5039,8 @@
       <c r="R126" s="25"/>
     </row>
     <row r="127" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B127" s="54"/>
-      <c r="C127" s="55" t="s">
+      <c r="B127" s="53"/>
+      <c r="C127" s="54" t="s">
         <v>124</v>
       </c>
       <c r="D127" s="25"/>
@@ -6176,8 +5060,8 @@
       <c r="R127" s="25"/>
     </row>
     <row r="128" spans="2:18" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B128" s="54"/>
-      <c r="C128" s="55" t="s">
+      <c r="B128" s="53"/>
+      <c r="C128" s="54" t="s">
         <v>125</v>
       </c>
       <c r="D128" s="25"/>
@@ -6198,7 +5082,7 @@
     </row>
     <row r="129" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B129" s="32"/>
-      <c r="C129" s="55" t="s">
+      <c r="C129" s="54" t="s">
         <v>126</v>
       </c>
       <c r="D129" s="25"/>
@@ -6221,7 +5105,7 @@
       <c r="B130" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C130" s="55" t="s">
+      <c r="C130" s="54" t="s">
         <v>128</v>
       </c>
       <c r="D130" s="25"/>
@@ -6262,19 +5146,19 @@
       <c r="R132" s="25"/>
     </row>
     <row r="133" spans="2:21" ht="66.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="85" t="s">
+      <c r="B133" s="79" t="s">
         <v>130</v>
       </c>
       <c r="C133" s="30"/>
       <c r="D133" s="32"/>
-      <c r="E133" s="58" t="s">
+      <c r="E133" s="57" t="s">
         <v>131</v>
       </c>
       <c r="F133" s="25"/>
       <c r="G133" s="25"/>
       <c r="H133" s="27"/>
-      <c r="I133" s="86" t="s">
-        <v>362</v>
+      <c r="I133" s="80" t="s">
+        <v>256</v>
       </c>
       <c r="J133" s="25"/>
       <c r="K133" s="25"/>
@@ -6287,14 +5171,14 @@
       <c r="R133" s="25"/>
     </row>
     <row r="134" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B134" s="56"/>
+      <c r="B134" s="55"/>
       <c r="C134" s="25"/>
       <c r="D134" s="36"/>
-      <c r="E134" s="57"/>
+      <c r="E134" s="56"/>
       <c r="F134" s="25"/>
       <c r="G134" s="25"/>
       <c r="H134" s="27"/>
-      <c r="I134" s="64"/>
+      <c r="I134" s="63"/>
       <c r="J134" s="25"/>
       <c r="K134" s="25"/>
       <c r="L134" s="25"/>
@@ -6306,14 +5190,14 @@
       <c r="R134" s="25"/>
     </row>
     <row r="135" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="56"/>
+      <c r="B135" s="55"/>
       <c r="C135" s="25"/>
       <c r="D135" s="36"/>
-      <c r="E135" s="57"/>
+      <c r="E135" s="56"/>
       <c r="F135" s="25"/>
       <c r="G135" s="25"/>
       <c r="H135" s="27"/>
-      <c r="I135" s="64"/>
+      <c r="I135" s="63"/>
       <c r="J135" s="25"/>
       <c r="K135" s="25"/>
       <c r="L135" s="25"/>
@@ -6324,18 +5208,18 @@
       <c r="Q135" s="25"/>
       <c r="R135" s="25"/>
       <c r="U135" s="3" t="s">
-        <v>363</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B136" s="56"/>
+      <c r="B136" s="55"/>
       <c r="C136" s="25"/>
       <c r="D136" s="36"/>
-      <c r="E136" s="57"/>
+      <c r="E136" s="56"/>
       <c r="F136" s="25"/>
       <c r="G136" s="25"/>
       <c r="H136" s="27"/>
-      <c r="I136" s="64"/>
+      <c r="I136" s="63"/>
       <c r="J136" s="25"/>
       <c r="K136" s="25"/>
       <c r="L136" s="25"/>
@@ -6346,18 +5230,18 @@
       <c r="Q136" s="25"/>
       <c r="R136" s="25"/>
       <c r="U136" s="3" t="s">
-        <v>364</v>
+        <v>258</v>
       </c>
     </row>
     <row r="137" spans="2:21" ht="28.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B137" s="56"/>
+      <c r="B137" s="55"/>
       <c r="C137" s="25"/>
       <c r="D137" s="36"/>
-      <c r="E137" s="57"/>
+      <c r="E137" s="56"/>
       <c r="F137" s="25"/>
       <c r="G137" s="25"/>
       <c r="H137" s="27"/>
-      <c r="I137" s="64"/>
+      <c r="I137" s="63"/>
       <c r="J137" s="25"/>
       <c r="K137" s="25"/>
       <c r="L137" s="25"/>
@@ -6411,7 +5295,7 @@
       <c r="R140" s="25"/>
     </row>
     <row r="141" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B141" s="87" t="s">
+      <c r="B141" s="81" t="s">
         <v>134</v>
       </c>
       <c r="C141" s="25"/>
@@ -6432,11 +5316,11 @@
       <c r="R141" s="25"/>
     </row>
     <row r="142" spans="2:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B142" s="59" t="s">
+      <c r="B142" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="C142" s="60"/>
-      <c r="D142" s="55" t="s">
+      <c r="C142" s="59"/>
+      <c r="D142" s="54" t="s">
         <v>136</v>
       </c>
       <c r="E142" s="25"/>
@@ -6456,9 +5340,9 @@
       <c r="T142" s="3"/>
     </row>
     <row r="143" spans="2:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B143" s="61"/>
-      <c r="C143" s="54"/>
-      <c r="D143" s="55" t="s">
+      <c r="B143" s="60"/>
+      <c r="C143" s="53"/>
+      <c r="D143" s="54" t="s">
         <v>137</v>
       </c>
       <c r="E143" s="25"/>
@@ -6478,9 +5362,9 @@
       <c r="T143" s="3"/>
     </row>
     <row r="144" spans="2:21" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B144" s="61"/>
-      <c r="C144" s="54"/>
-      <c r="D144" s="55" t="s">
+      <c r="B144" s="60"/>
+      <c r="C144" s="53"/>
+      <c r="D144" s="54" t="s">
         <v>138</v>
       </c>
       <c r="E144" s="25"/>
@@ -6502,7 +5386,7 @@
     <row r="145" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B145" s="30"/>
       <c r="C145" s="32"/>
-      <c r="D145" s="55" t="s">
+      <c r="D145" s="54" t="s">
         <v>139</v>
       </c>
       <c r="E145" s="25"/>
@@ -6525,11 +5409,11 @@
       <c r="T145" s="3"/>
     </row>
     <row r="146" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B146" s="59" t="s">
+      <c r="B146" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="C146" s="60"/>
-      <c r="D146" s="55" t="s">
+      <c r="C146" s="59"/>
+      <c r="D146" s="54" t="s">
         <v>141</v>
       </c>
       <c r="E146" s="25"/>
@@ -6549,9 +5433,9 @@
       <c r="T146" s="3"/>
     </row>
     <row r="147" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B147" s="61"/>
-      <c r="C147" s="54"/>
-      <c r="D147" s="55" t="s">
+      <c r="B147" s="60"/>
+      <c r="C147" s="53"/>
+      <c r="D147" s="54" t="s">
         <v>142</v>
       </c>
       <c r="E147" s="25"/>
@@ -6571,9 +5455,9 @@
       <c r="T147" s="3"/>
     </row>
     <row r="148" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B148" s="61"/>
-      <c r="C148" s="54"/>
-      <c r="D148" s="55" t="s">
+      <c r="B148" s="60"/>
+      <c r="C148" s="53"/>
+      <c r="D148" s="54" t="s">
         <v>143</v>
       </c>
       <c r="E148" s="25"/>
@@ -6595,7 +5479,7 @@
     <row r="149" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B149" s="30"/>
       <c r="C149" s="32"/>
-      <c r="D149" s="55" t="s">
+      <c r="D149" s="54" t="s">
         <v>144</v>
       </c>
       <c r="E149" s="25"/>
@@ -6618,11 +5502,11 @@
       <c r="T149" s="3"/>
     </row>
     <row r="150" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B150" s="59" t="s">
+      <c r="B150" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="C150" s="60"/>
-      <c r="D150" s="55" t="s">
+      <c r="C150" s="59"/>
+      <c r="D150" s="54" t="s">
         <v>146</v>
       </c>
       <c r="E150" s="25"/>
@@ -6644,7 +5528,7 @@
     <row r="151" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B151" s="30"/>
       <c r="C151" s="32"/>
-      <c r="D151" s="55" t="s">
+      <c r="D151" s="54" t="s">
         <v>147</v>
       </c>
       <c r="E151" s="25"/>
@@ -6664,11 +5548,11 @@
       <c r="T151" s="3"/>
     </row>
     <row r="152" spans="2:20" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B152" s="63" t="s">
+      <c r="B152" s="62" t="s">
         <v>148</v>
       </c>
       <c r="C152" s="36"/>
-      <c r="D152" s="55" t="s">
+      <c r="D152" s="54" t="s">
         <v>149</v>
       </c>
       <c r="E152" s="25"/>
@@ -6709,7 +5593,7 @@
       <c r="R154" s="25"/>
     </row>
     <row r="155" spans="2:20" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B155" s="78" t="s">
+      <c r="B155" s="72" t="s">
         <v>151</v>
       </c>
       <c r="C155" s="25"/>
@@ -6771,7 +5655,7 @@
       <c r="K157" s="34"/>
       <c r="L157" s="25"/>
       <c r="M157" s="36"/>
-      <c r="N157" s="62"/>
+      <c r="N157" s="61"/>
       <c r="O157" s="25"/>
       <c r="P157" s="25"/>
       <c r="Q157" s="25"/>
@@ -6790,7 +5674,7 @@
       <c r="K158" s="34"/>
       <c r="L158" s="25"/>
       <c r="M158" s="36"/>
-      <c r="N158" s="62"/>
+      <c r="N158" s="61"/>
       <c r="O158" s="25"/>
       <c r="P158" s="25"/>
       <c r="Q158" s="25"/>
@@ -6809,7 +5693,7 @@
       <c r="K159" s="34"/>
       <c r="L159" s="25"/>
       <c r="M159" s="36"/>
-      <c r="N159" s="62"/>
+      <c r="N159" s="61"/>
       <c r="O159" s="25"/>
       <c r="P159" s="25"/>
       <c r="Q159" s="25"/>
@@ -6828,14 +5712,14 @@
       <c r="K160" s="34"/>
       <c r="L160" s="25"/>
       <c r="M160" s="36"/>
-      <c r="N160" s="62"/>
+      <c r="N160" s="61"/>
       <c r="O160" s="25"/>
       <c r="P160" s="25"/>
       <c r="Q160" s="25"/>
       <c r="R160" s="25"/>
     </row>
     <row r="162" spans="2:18" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B162" s="50" t="s">
+      <c r="B162" s="24" t="s">
         <v>157</v>
       </c>
       <c r="C162" s="25"/>
@@ -6853,10 +5737,10 @@
       <c r="O162" s="25"/>
       <c r="P162" s="25"/>
       <c r="Q162" s="25"/>
-      <c r="R162" s="36"/>
+      <c r="R162" s="25"/>
     </row>
     <row r="163" spans="2:18" ht="42.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B163" s="43" t="s">
+      <c r="B163" s="82" t="s">
         <v>158</v>
       </c>
       <c r="C163" s="25"/>
@@ -6866,8 +5750,8 @@
       <c r="G163" s="25"/>
       <c r="H163" s="25"/>
       <c r="I163" s="25"/>
-      <c r="J163" s="36"/>
-      <c r="K163" s="45" t="s">
+      <c r="J163" s="27"/>
+      <c r="K163" s="28" t="s">
         <v>159</v>
       </c>
       <c r="L163" s="25"/>
@@ -6876,10 +5760,10 @@
       <c r="O163" s="25"/>
       <c r="P163" s="25"/>
       <c r="Q163" s="25"/>
-      <c r="R163" s="36"/>
+      <c r="R163" s="25"/>
     </row>
     <row r="164" spans="2:18" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="35"/>
+      <c r="B164" s="81"/>
       <c r="C164" s="25"/>
       <c r="D164" s="25"/>
       <c r="E164" s="25"/>
@@ -6887,18 +5771,18 @@
       <c r="G164" s="25"/>
       <c r="H164" s="25"/>
       <c r="I164" s="25"/>
-      <c r="J164" s="36"/>
-      <c r="K164" s="45"/>
+      <c r="J164" s="27"/>
+      <c r="K164" s="28"/>
       <c r="L164" s="25"/>
       <c r="M164" s="25"/>
       <c r="N164" s="25"/>
       <c r="O164" s="25"/>
       <c r="P164" s="25"/>
       <c r="Q164" s="25"/>
-      <c r="R164" s="36"/>
+      <c r="R164" s="25"/>
     </row>
     <row r="165" spans="2:18" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B165" s="35"/>
+      <c r="B165" s="81"/>
       <c r="C165" s="25"/>
       <c r="D165" s="25"/>
       <c r="E165" s="25"/>
@@ -6906,18 +5790,18 @@
       <c r="G165" s="25"/>
       <c r="H165" s="25"/>
       <c r="I165" s="25"/>
-      <c r="J165" s="36"/>
-      <c r="K165" s="45"/>
+      <c r="J165" s="27"/>
+      <c r="K165" s="28"/>
       <c r="L165" s="25"/>
       <c r="M165" s="25"/>
       <c r="N165" s="25"/>
       <c r="O165" s="25"/>
       <c r="P165" s="25"/>
       <c r="Q165" s="25"/>
-      <c r="R165" s="36"/>
+      <c r="R165" s="25"/>
     </row>
     <row r="166" spans="2:18" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B166" s="35"/>
+      <c r="B166" s="81"/>
       <c r="C166" s="25"/>
       <c r="D166" s="25"/>
       <c r="E166" s="25"/>
@@ -6925,18 +5809,18 @@
       <c r="G166" s="25"/>
       <c r="H166" s="25"/>
       <c r="I166" s="25"/>
-      <c r="J166" s="36"/>
-      <c r="K166" s="45"/>
+      <c r="J166" s="27"/>
+      <c r="K166" s="28"/>
       <c r="L166" s="25"/>
       <c r="M166" s="25"/>
       <c r="N166" s="25"/>
       <c r="O166" s="25"/>
       <c r="P166" s="25"/>
       <c r="Q166" s="25"/>
-      <c r="R166" s="36"/>
+      <c r="R166" s="25"/>
     </row>
     <row r="167" spans="2:18" ht="28.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B167" s="35"/>
+      <c r="B167" s="81"/>
       <c r="C167" s="25"/>
       <c r="D167" s="25"/>
       <c r="E167" s="25"/>
@@ -6944,15 +5828,15 @@
       <c r="G167" s="25"/>
       <c r="H167" s="25"/>
       <c r="I167" s="25"/>
-      <c r="J167" s="36"/>
-      <c r="K167" s="45"/>
+      <c r="J167" s="27"/>
+      <c r="K167" s="28"/>
       <c r="L167" s="25"/>
       <c r="M167" s="25"/>
       <c r="N167" s="25"/>
       <c r="O167" s="25"/>
       <c r="P167" s="25"/>
       <c r="Q167" s="25"/>
-      <c r="R167" s="36"/>
+      <c r="R167" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="445">
@@ -7403,7 +6287,7 @@
     <mergeCell ref="K9:R9"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4:R4 O120:R122" xr:uid="{00000000-0002-0000-1100-000000000000}">
       <formula1>"여,부"</formula1>
     </dataValidation>
@@ -7451,7 +6335,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="22.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="24" t="s">
         <v>160</v>
       </c>
       <c r="C2" s="25"/>
@@ -7469,10 +6353,10 @@
       <c r="O2" s="25"/>
       <c r="P2" s="25"/>
       <c r="Q2" s="25"/>
-      <c r="R2" s="36"/>
+      <c r="R2" s="25"/>
     </row>
     <row r="3" spans="2:18" ht="22.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="24" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="25"/>
@@ -7490,14 +6374,14 @@
       <c r="O3" s="25"/>
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
-      <c r="R3" s="36"/>
+      <c r="R3" s="25"/>
     </row>
     <row r="4" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="83" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="55" t="s">
+      <c r="C4" s="53"/>
+      <c r="D4" s="54" t="s">
         <v>163</v>
       </c>
       <c r="E4" s="25"/>
@@ -7509,16 +6393,16 @@
       <c r="K4" s="25"/>
       <c r="L4" s="25"/>
       <c r="M4" s="25"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="45"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="28"/>
       <c r="P4" s="25"/>
       <c r="Q4" s="25"/>
-      <c r="R4" s="36"/>
+      <c r="R4" s="25"/>
     </row>
     <row r="5" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="66"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="55" t="s">
+      <c r="B5" s="65"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="54" t="s">
         <v>164</v>
       </c>
       <c r="E5" s="25"/>
@@ -7530,16 +6414,16 @@
       <c r="K5" s="25"/>
       <c r="L5" s="25"/>
       <c r="M5" s="25"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="34"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="71"/>
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
-      <c r="R5" s="36"/>
+      <c r="R5" s="25"/>
     </row>
     <row r="6" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="30"/>
       <c r="C6" s="32"/>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="54" t="s">
         <v>165</v>
       </c>
       <c r="E6" s="25"/>
@@ -7551,18 +6435,18 @@
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="34"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="71"/>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
-      <c r="R6" s="36"/>
+      <c r="R6" s="25"/>
     </row>
     <row r="7" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="55" t="s">
+      <c r="C7" s="59"/>
+      <c r="D7" s="54" t="s">
         <v>167</v>
       </c>
       <c r="E7" s="25"/>
@@ -7574,18 +6458,18 @@
       <c r="K7" s="25"/>
       <c r="L7" s="25"/>
       <c r="M7" s="25"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="68" t="s">
-        <v>320</v>
-      </c>
-      <c r="P7" s="69"/>
-      <c r="Q7" s="69"/>
-      <c r="R7" s="70"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="66" t="s">
+        <v>214</v>
+      </c>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
     </row>
     <row r="8" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="66"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55" t="s">
+      <c r="B8" s="65"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="54" t="s">
         <v>168</v>
       </c>
       <c r="E8" s="25"/>
@@ -7597,16 +6481,16 @@
       <c r="K8" s="25"/>
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="73"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+      <c r="Q8" s="69"/>
+      <c r="R8" s="69"/>
     </row>
     <row r="9" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="66"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="55" t="s">
+      <c r="B9" s="65"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="54" t="s">
         <v>169</v>
       </c>
       <c r="E9" s="25"/>
@@ -7618,16 +6502,16 @@
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="73"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+      <c r="Q9" s="69"/>
+      <c r="R9" s="69"/>
     </row>
     <row r="10" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="30"/>
       <c r="C10" s="32"/>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="54" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="25"/>
@@ -7639,18 +6523,18 @@
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="73"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="69"/>
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
     </row>
     <row r="11" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="55" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="54" t="s">
         <v>172</v>
       </c>
       <c r="E11" s="25"/>
@@ -7662,16 +6546,16 @@
       <c r="K11" s="25"/>
       <c r="L11" s="25"/>
       <c r="M11" s="25"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="73"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
     </row>
     <row r="12" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="66"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="55" t="s">
+      <c r="B12" s="65"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="54" t="s">
         <v>173</v>
       </c>
       <c r="E12" s="25"/>
@@ -7683,16 +6567,16 @@
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
       <c r="M12" s="25"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="73"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
     </row>
     <row r="13" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="30"/>
       <c r="C13" s="32"/>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="54" t="s">
         <v>174</v>
       </c>
       <c r="E13" s="25"/>
@@ -7704,15 +6588,15 @@
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74"/>
-      <c r="R13" s="47"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
     </row>
     <row r="14" spans="2:18" ht="4.95" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="15" spans="2:18" ht="22.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="50" t="s">
+      <c r="B15" s="24" t="s">
         <v>175</v>
       </c>
       <c r="C15" s="25"/>
@@ -7730,10 +6614,10 @@
       <c r="O15" s="25"/>
       <c r="P15" s="25"/>
       <c r="Q15" s="25"/>
-      <c r="R15" s="36"/>
+      <c r="R15" s="25"/>
     </row>
     <row r="16" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="84" t="s">
         <v>176</v>
       </c>
       <c r="C16" s="25"/>
@@ -7747,14 +6631,14 @@
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="45"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="63"/>
       <c r="P16" s="25"/>
       <c r="Q16" s="25"/>
-      <c r="R16" s="36"/>
+      <c r="R16" s="25"/>
     </row>
     <row r="17" spans="2:18" ht="33.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="85" t="s">
         <v>177</v>
       </c>
       <c r="C17" s="25"/>
@@ -7768,14 +6652,14 @@
       <c r="K17" s="25"/>
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="34"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="33"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
-      <c r="R17" s="36"/>
+      <c r="R17" s="25"/>
     </row>
     <row r="18" spans="2:18" ht="25.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="84" t="s">
         <v>178</v>
       </c>
       <c r="C18" s="25"/>
@@ -7789,11 +6673,11 @@
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="34"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="33"/>
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
-      <c r="R18" s="36"/>
+      <c r="R18" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="26">
